--- a/KatalonData/ABPTestDataDemo/ABPTestData_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/ABPTestData_Demo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\ABPTestDataDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543E7AF3-6616-4B36-857C-B6C9FB3D0F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543CDB0D-D85A-454C-99D7-D6A0AAB64DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="13" activeTab="14" xr2:uid="{1DD8A320-6572-432F-97F4-1D86BCB29215}"/>
   </bookViews>
@@ -32,7 +32,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="79">
   <si>
     <t>Result</t>
   </si>
@@ -278,9 +278,6 @@
   </si>
   <si>
     <t>Password must contain at least one alpha character and one numeric character.</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 22:24:55 IST 2026</t>
   </si>
   <si>
     <t>Create Account Profile,
@@ -310,9 +307,6 @@
 State :</t>
   </si>
   <si>
-    <t>Wed Jul 22 15:20:36 IST 2026</t>
-  </si>
-  <si>
     <t>* Indicates required field,
 Role: *,	
  What's this?,
@@ -329,33 +323,6 @@
 Text Delivery Options:</t>
   </si>
   <si>
-    <t>Wed Jul 22 15:27:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 22 15:29:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 22 15:30:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 22 15:32:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 22 15:33:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 22 15:34:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 22 15:44:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 22 18:02:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 22 18:10:16 IST 2026</t>
-  </si>
-  <si>
     <t>Thu Jul 30 15:18:49 IST 2026</t>
   </si>
   <si>
@@ -368,91 +335,55 @@
     <t>Username cannot contain any spaces or special characters.</t>
   </si>
   <si>
-    <t>Tue Aug 25 16:50:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 16:52:23 IST 2026</t>
-  </si>
-  <si>
     <t>Password must be at least 8 characters long and no more than 32 characters long.,Password must contain at least one alpha character and one numeric character.,The password must also contain at least one special character.</t>
   </si>
   <si>
-    <t>Tue Aug 25 16:57:08 IST 2026</t>
-  </si>
-  <si>
     <t>Password must contain at least one alpha character and one numeric character.,The password must also contain at least one special character.</t>
   </si>
   <si>
-    <t>Tue Aug 25 16:59:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:46:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:46:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:46:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:47:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:47:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:47:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:48:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:48:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:48:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:49:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:49:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:49:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:50:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:59:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:59:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 19:00:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 19:00:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 21:17:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Sep 18 02:30:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Sep 18 02:30:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Sep 18 02:30:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Sep 18 02:31:20 IST 2026</t>
+    <t>Thu Oct 08 01:52:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:52:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:53:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:54:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 01:55:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 02:15:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 14:13:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 14:15:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 14:18:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 14:20:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 14:58:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 15:00:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 15:10:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 15:11:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 15:11:43 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -930,7 +861,7 @@
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" customWidth="true" width="19.26953125" collapsed="true"/>
+    <col min="5" max="5" width="19.26953125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -1003,7 +934,7 @@
         <v>398902</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J2" s="6" t="s">
         <v>18</v>
@@ -1033,9 +964,9 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" customWidth="true" width="23.08984375" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" width="33.0" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" width="22.36328125" collapsed="true"/>
+    <col min="5" max="5" width="23.08984375" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="33" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="22.36328125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -1071,11 +1002,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="269" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>66</v>
+      <c r="B2" t="s">
+        <v>73</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1086,7 +1017,7 @@
       </c>
       <c r="F2" s="15" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>08/26/2026</v>
+        <v>10/13/2026</v>
       </c>
       <c r="G2" s="16">
         <v>12</v>
@@ -1102,11 +1033,11 @@
  Individual Amount:,	Repeat this amount until the Balance Due is achieved: $, 
 12.00,
 Step 4: Review Payment Plan,
-1 Deferred payment of $12.00 on 08/26/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 08/26/2026</v>
+1 Deferred payment of $12.00 on 10/13/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/13/2026</v>
       </c>
       <c r="J2" s="19" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(H2,"0.00")&amp;" starting on "&amp;F2</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 08/26/2026</v>
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/13/2026</v>
       </c>
     </row>
   </sheetData>
@@ -1119,12 +1050,12 @@
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" style="11" width="8.7265625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="11" width="23.453125" collapsed="true"/>
-    <col min="7" max="9" style="11" width="8.7265625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="11" width="35.0" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="11" width="30.453125" collapsed="true"/>
-    <col min="12" max="16384" style="11" width="8.7265625" collapsed="true"/>
+    <col min="1" max="5" width="8.7265625" style="11" collapsed="1"/>
+    <col min="6" max="6" width="23.453125" style="11" customWidth="1" collapsed="1"/>
+    <col min="7" max="9" width="8.7265625" style="11" collapsed="1"/>
+    <col min="10" max="10" width="35" style="11" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="30.453125" style="11" customWidth="1" collapsed="1"/>
+    <col min="12" max="16384" width="8.7265625" style="11" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1167,7 +1098,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1181,7 +1112,7 @@
       </c>
       <c r="G2" s="15" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>08/26/2026</v>
+        <v>10/13/2026</v>
       </c>
       <c r="H2" s="16">
         <v>12</v>
@@ -1196,7 +1127,7 @@
 Daily,
 Select the date you wish to submit your first payment and it will recur every day after,
 Step 4: Review Payment Plan,
-Daily payments of $12.00 starting on 08/26/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 08/26/2026 ,Individual Convenience Fee Amount:,	
+Daily payments of $12.00 starting on 10/13/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 10/13/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1204,7 +1135,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(I2,"0.00")&amp;" starting on "&amp;G2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 08/26/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 10/13/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1255,11 +1186,11 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>68</v>
+      <c r="B2" t="s">
+        <v>75</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1273,7 +1204,7 @@
       </c>
       <c r="G2" s="15" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>08/26/2026</v>
+        <v>10/13/2026</v>
       </c>
       <c r="H2" s="16">
         <v>12</v>
@@ -1287,7 +1218,7 @@
 Deferred,
 Select the date you wish to submit your payment,
 Step 4: Review Payment Plan,
-1 Deferred payment of $12.00 on 08/26/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 08/26/2026 ,Individual Convenience Fee Amount:,	
+1 Deferred payment of $12.00 on 10/13/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/13/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1295,7 +1226,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(I2,"0.00")&amp;" starting on "&amp;G2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 08/26/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 10/13/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1328,11 +1259,11 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>70</v>
+      <c r="B2" t="s">
+        <v>59</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1370,11 +1301,11 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>69</v>
+      <c r="B2" t="s">
+        <v>58</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1394,13 +1325,13 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="11" width="8.7265625"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="11" width="25.36328125"/>
-    <col min="3" max="4" style="11" width="8.7265625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="11" width="11.90625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="11" width="19.81640625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="11" width="79.6328125" collapsed="true"/>
-    <col min="8" max="16384" style="11" width="8.7265625"/>
+    <col min="1" max="1" width="8.7265625" style="11"/>
+    <col min="2" max="2" width="25.36328125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.7265625" style="11"/>
+    <col min="5" max="5" width="11.90625" style="11" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="19.81640625" style="11" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="79.6328125" style="11" customWidth="1" collapsed="1"/>
+    <col min="8" max="16384" width="8.7265625" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1431,7 +1362,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1444,7 +1375,7 @@
         <v>25</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1452,7 +1383,7 @@
         <v>24</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>16</v>
@@ -1461,7 +1392,7 @@
         <v>53</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1469,7 +1400,7 @@
         <v>24</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>16</v>
@@ -1491,8 +1422,8 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="55.1796875"/>
-    <col min="7" max="7" customWidth="true" width="15.6328125"/>
+    <col min="6" max="6" width="55.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25" x14ac:dyDescent="0.25">
@@ -1519,11 +1450,11 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>101</v>
+      <c r="B2" t="s">
+        <v>69</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1532,11 +1463,11 @@
       <c r="E2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F2" t="s" s="0">
-        <v>72</v>
-      </c>
-      <c r="G2" t="s" s="0">
-        <v>71</v>
+      <c r="F2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1549,12 +1480,12 @@
   <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="25.1796875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" width="10.08984375" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" width="16.90625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" width="11.81640625" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" width="15.1796875" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" width="12.08984375" collapsed="true"/>
+    <col min="2" max="2" width="25.1796875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="10.08984375" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="16.90625" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="11.81640625" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.1796875" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="12.08984375" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="11" customFormat="1" ht="25" x14ac:dyDescent="0.25">
@@ -1599,11 +1530,11 @@
       </c>
     </row>
     <row r="2" spans="1:13" s="11" customFormat="1" ht="300" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>58</v>
+      <c r="B2" t="s">
+        <v>64</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1647,14 +1578,14 @@
   <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="16.36328125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="11" width="7.81640625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="11" width="25.1796875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="11" width="8.08984375" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="11" width="8.7265625" collapsed="true"/>
-    <col min="5" max="11" style="11" width="16.36328125" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="11" width="10.1796875" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="11" width="9.54296875" collapsed="true"/>
-    <col min="14" max="16384" style="11" width="16.36328125" collapsed="true"/>
+    <col min="1" max="1" width="7.81640625" style="11" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="25.1796875" style="11" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="8.08984375" style="11" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="8.7265625" style="11" customWidth="1" collapsed="1"/>
+    <col min="5" max="11" width="16.36328125" style="11" collapsed="1"/>
+    <col min="12" max="12" width="10.1796875" style="11" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="9.54296875" style="11" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="16.36328125" style="11" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1703,7 +1634,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1713,7 +1644,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>31</v>
@@ -1747,14 +1678,14 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="8" width="6.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="8" width="25.1796875" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="8" width="5.90625" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="8" width="8.0" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="8" width="17.0" collapsed="true"/>
-    <col min="6" max="8" bestFit="true" customWidth="true" style="8" width="12.36328125" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="8" width="14.0" collapsed="true"/>
-    <col min="10" max="16384" style="8" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6" style="8" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="25.1796875" style="8" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="5.90625" style="8" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="8" style="8" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="17" style="8" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="8" width="12.36328125" style="8" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="14" style="8" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="16384" width="8.7265625" style="8" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1791,7 +1722,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>16</v>
@@ -1822,7 +1753,7 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" customWidth="true" width="50.453125" collapsed="true"/>
+    <col min="6" max="6" width="50.453125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1846,11 +1777,11 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>61</v>
+      <c r="B2" t="s">
+        <v>67</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1873,8 +1804,8 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultColWidth="20.7265625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="11" width="11.08984375" collapsed="true"/>
-    <col min="2" max="16384" style="11" width="20.7265625" collapsed="true"/>
+    <col min="1" max="1" width="11.08984375" style="11" customWidth="1" collapsed="1"/>
+    <col min="2" max="16384" width="20.7265625" style="11" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1905,7 +1836,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1931,8 +1862,8 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" customWidth="true" width="24.7265625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" width="23.7265625" collapsed="true"/>
+    <col min="6" max="6" width="24.7265625" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="23.7265625" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1959,11 +1890,11 @@
       </c>
     </row>
     <row r="2" spans="1:7" s="3" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>63</v>
+      <c r="B2" t="s">
+        <v>70</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1982,7 +1913,7 @@
 Select the date you wish to submit your first payment and it will recur every year on that day,
 Divide your payment plan by...,
 Number of Payments:,Divide the Balance Due into,
-Individual Amount:,Repeat this amount until the Balance Due is achieved: $,1 Annual payment of $12.00 on 08/26/2026</v>
+Individual Amount:,Repeat this amount until the Balance Due is achieved: $,1 Annual payment of $12.00 on 10/13/2026</v>
       </c>
     </row>
   </sheetData>
@@ -1995,9 +1926,9 @@
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" customWidth="true" width="30.36328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" width="34.0" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" width="23.1796875" collapsed="true"/>
+    <col min="6" max="6" width="30.36328125" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="34" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="23.1796875" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
@@ -2036,11 +1967,11 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="241" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>64</v>
+      <c r="B2" t="s">
+        <v>71</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -2054,7 +1985,7 @@
       </c>
       <c r="G2" s="15" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>08/26/2026</v>
+        <v>10/13/2026</v>
       </c>
       <c r="H2" s="16">
         <v>12</v>
@@ -2071,11 +2002,11 @@
 Number of Payments:,Divide the Balance Due into ,
 Individual Amount:,Repeat this amount until the Balance Due is achieved: $, 
 Step 4: Review Payment Plan,
-1 Daily payment of $12.00 on 08/26/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 08/26/2026</v>
+1 Daily payment of $12.00 on 10/13/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/13/2026</v>
       </c>
       <c r="K2" s="19" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(I2,"0.00")&amp;" starting on "&amp;G2</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 08/26/2026</v>
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 10/13/2026</v>
       </c>
     </row>
   </sheetData>
@@ -2088,10 +2019,10 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" style="11" width="8.7265625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="11" width="37.6328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="11" width="36.90625" collapsed="true"/>
-    <col min="8" max="16384" style="11" width="8.7265625" collapsed="true"/>
+    <col min="1" max="5" width="8.7265625" style="11" collapsed="1"/>
+    <col min="6" max="6" width="37.6328125" style="11" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="36.90625" style="11" customWidth="1" collapsed="1"/>
+    <col min="8" max="16384" width="8.7265625" style="11" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -2122,7 +2053,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -2144,7 +2075,7 @@
 Number of Payments:,Divide the Balance Due into, 
 Individual Amount:,	Repeat this amount until the Balance Due is achieved: $ ,
 Step 4: Review Payment Plan
-1 Quarterly payment of $12.00 on 08/26/2026</v>
+1 Quarterly payment of $12.00 on 10/13/2026</v>
       </c>
     </row>
   </sheetData>
